--- a/country_correlation_analysis/country_correlation_all_models.xlsx
+++ b/country_correlation_analysis/country_correlation_all_models.xlsx
@@ -467,7 +467,7 @@
         <v>0.952786570034668</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5525291025336792</v>
+        <v>0.552529102533679</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5610184511231918</v>
+        <v>0.5610184511231919</v>
       </c>
       <c r="E3" t="n">
         <v>0.5716381013615186</v>
@@ -499,7 +499,7 @@
         <v>0.952786570034668</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5610184511231918</v>
+        <v>0.5610184511231919</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5525291025336792</v>
+        <v>0.552529102533679</v>
       </c>
       <c r="C5" t="n">
         <v>0.5716381013615186</v>

--- a/country_correlation_analysis/country_correlation_all_models.xlsx
+++ b/country_correlation_analysis/country_correlation_all_models.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,15 +437,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -461,69 +471,143 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5378456091261165</v>
+        <v>0.9587723711316434</v>
       </c>
       <c r="D2" t="n">
-        <v>0.952786570034668</v>
+        <v>0.9780887021703472</v>
       </c>
       <c r="E2" t="n">
-        <v>0.552529102533679</v>
+        <v>0.9828467227620172</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9851054638823976</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9605471027428529</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5378456091261165</v>
+        <v>0.9587723711316434</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5610184511231919</v>
+        <v>0.9485806804991254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5716381013615186</v>
+        <v>0.9446204149955574</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9382233221535661</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8953331617367897</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.952786570034668</v>
+        <v>0.9780887021703472</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5610184511231919</v>
+        <v>0.9485806804991254</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6991135488592624</v>
+        <v>0.9441614805351882</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9464742483981714</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8972159259875406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9828467227620172</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9446204149955574</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9441614805351882</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9994482425786506</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.989200832564511</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9851054638823976</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9382233221535661</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9464742483981714</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9994482425786506</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9906737133727557</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.552529102533679</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.5716381013615186</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.6991135488592624</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B7" t="n">
+        <v>0.9605471027428529</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8953331617367897</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8972159259875406</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.989200832564511</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9906737133727557</v>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -538,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,15 +633,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -573,69 +667,143 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2710250102769239</v>
+        <v>0.002514538414455129</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00329104003714503</v>
+        <v>0.0007148975973477708</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2555467115593542</v>
+        <v>0.0004388288334266921</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0003311186536254791</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.002304091822152459</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2710250102769239</v>
+        <v>0.002514538414455129</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2467602745356119</v>
+        <v>0.003897944664096111</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2359399731406196</v>
+        <v>0.004515425871598556</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005606655931550493</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01585940024675064</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00329104003714503</v>
+        <v>0.0007148975973477708</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2467602745356119</v>
+        <v>0.003897944664096111</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1221789598597857</v>
+        <v>0.00458985980019522</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.00422083332480156</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01530391424572156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0004388288334266921</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.004515425871598556</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00458985980019522</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.565703905404973e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.000174303315603848</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0003311186536254791</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.005606655931550493</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00422083332480156</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.565703905404973e-07</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0001300638349363417</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.2555467115593542</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.2359399731406196</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.1221789598597857</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B7" t="n">
+        <v>0.002304091822152459</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01585940024675064</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01530391424572156</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.000174303315603848</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0001300638349363417</v>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
     </row>
